--- a/utils/monday_sprint_sprint_2023-15.xlsx
+++ b/utils/monday_sprint_sprint_2023-15.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="134">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>21171</t>
+    <t>4812056857</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>14/07/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>30/07/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,13 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>21209</t>
+    <t>4812104626</t>
   </si>
   <si>
     <t>Melhoria Radiografia</t>
   </si>
   <si>
-    <t>20686</t>
+    <t>4735948848</t>
   </si>
   <si>
     <t>Alteração do Fluxo 102</t>
@@ -117,61 +117,76 @@
     <t>30/06/2023</t>
   </si>
   <si>
+    <t>17/07/2023</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
     <t>Junho</t>
   </si>
   <si>
-    <t>20974</t>
+    <t>4735045770</t>
   </si>
   <si>
     <t>Melhoria no sistema de análise crítica para partículas magnéticas</t>
   </si>
   <si>
-    <t>21068</t>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>4811844793</t>
   </si>
   <si>
     <t>Melhoria sistema de movimentação</t>
   </si>
   <si>
-    <t>19480</t>
+    <t>4811919121</t>
   </si>
   <si>
     <t>Relatório Diário de Refugos</t>
   </si>
   <si>
-    <t>19329</t>
+    <t>4811993819</t>
   </si>
   <si>
     <t>Relatório Apontamentos Acabamento USE</t>
   </si>
   <si>
-    <t>21168</t>
+    <t>29/07/2023</t>
+  </si>
+  <si>
+    <t>4812041266</t>
   </si>
   <si>
     <t>Melhorias nos formulários de Análise Crítica</t>
   </si>
   <si>
-    <t>21236</t>
+    <t>25/07/2023</t>
+  </si>
+  <si>
+    <t>4812371666</t>
   </si>
   <si>
     <t>Sistema de desmoldagem USE</t>
   </si>
   <si>
-    <t>21216</t>
+    <t>27/07/2023</t>
+  </si>
+  <si>
+    <t>4812605907</t>
   </si>
   <si>
     <t>Criar uma flag no cadastro de usuários para liberar a movimentação sem registro</t>
   </si>
   <si>
-    <t>20965</t>
+    <t>4735118253</t>
   </si>
   <si>
     <t>Bloqueio de movimentação - END</t>
   </si>
   <si>
-    <t>20131</t>
+    <t>4668631647</t>
   </si>
   <si>
     <t>Informações de Desmoldagem e outras informações sobre o CPP</t>
@@ -186,55 +201,52 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>21207</t>
+    <t>4812086860</t>
   </si>
   <si>
     <t>Relatório Etiqueta Sistema Invoice</t>
   </si>
   <si>
-    <t>21250</t>
+    <t>4810792336</t>
   </si>
   <si>
     <t>Melhoria no relatório de FUP</t>
   </si>
   <si>
-    <t>21247</t>
+    <t>19/07/2023</t>
+  </si>
+  <si>
+    <t>4812216628</t>
   </si>
   <si>
     <t>Projeto FATURA - Criar nova coluna de data na planilha de cenários, unificando a informação de data lote e prazo ajustado</t>
   </si>
   <si>
-    <t>21111</t>
+    <t>4812791891</t>
   </si>
   <si>
     <t>Cadastrar Forno 10</t>
   </si>
   <si>
-    <t>21234</t>
+    <t>4819799066</t>
   </si>
   <si>
     <t>Parametrização inicial CenciHUB</t>
   </si>
   <si>
-    <t>17/07/2023</t>
-  </si>
-  <si>
-    <t>20862</t>
+    <t>4735266470</t>
   </si>
   <si>
     <t>SISTEMA DE CRIAÇÃO DE RETRABALHOS - Parte 2</t>
   </si>
   <si>
-    <t>21088</t>
+    <t>4837546198</t>
   </si>
   <si>
     <t>Adequação do formulário de ensaio destrutivo na analise critica</t>
   </si>
   <si>
-    <t>19/07/2023</t>
-  </si>
-  <si>
-    <t>19378</t>
+    <t>4823605055</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -243,24 +255,33 @@
     <t>Personalizar o layout - Testar Etiquetas</t>
   </si>
   <si>
-    <t>21224</t>
+    <t>4812114551</t>
   </si>
   <si>
     <t>Melhorias continuas lançamento NFs</t>
   </si>
   <si>
+    <t>4837551456</t>
+  </si>
+  <si>
     <t>Migrar dados para o CPP</t>
   </si>
   <si>
+    <t>4837567588</t>
+  </si>
+  <si>
     <t>Utilizar as tabelas CPP45 e CPP451</t>
   </si>
   <si>
-    <t>21268</t>
+    <t>4813029312</t>
   </si>
   <si>
     <t>Alteração Extrações de Cálculo Novo Custeio</t>
   </si>
   <si>
+    <t>24/07/2023</t>
+  </si>
+  <si>
     <t>4823318061</t>
   </si>
   <si>
@@ -279,6 +300,9 @@
     <t>03/08/2023</t>
   </si>
   <si>
+    <t>07/08/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
@@ -303,7 +327,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-15</t>
+    <t>Jun/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -367,6 +391,9 @@
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
   <si>
     <t>Baixa</t>
@@ -995,7 +1022,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1004,15 +1031,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1024,10 +1051,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1042,7 +1069,7 @@
         <v>33</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1051,15 +1078,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1071,10 +1098,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1106,7 +1133,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1118,10 +1145,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1136,7 +1163,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1153,7 +1180,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1165,10 +1192,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1183,7 +1210,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1200,7 +1227,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1212,10 +1239,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1230,7 +1257,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1247,7 +1274,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1259,10 +1286,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1277,7 +1304,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1294,7 +1321,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1306,10 +1333,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1324,7 +1351,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1341,7 +1368,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1353,10 +1380,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1371,7 +1398,7 @@
         <v>33</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1380,15 +1407,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1400,13 +1427,13 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -1415,10 +1442,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1427,15 +1454,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1447,10 +1474,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1465,7 +1492,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1482,7 +1509,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1494,10 +1521,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1512,7 +1539,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1529,7 +1556,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1541,10 +1568,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1559,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1576,7 +1603,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1588,10 +1615,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1623,7 +1650,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1635,10 +1662,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1650,10 +1677,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1662,7 +1689,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1670,7 +1697,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1682,10 +1709,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1709,15 +1736,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1729,10 +1756,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1744,10 +1771,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1756,7 +1783,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1764,25 +1791,25 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1791,10 +1818,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1803,7 +1830,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1811,7 +1838,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1823,10 +1850,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1841,7 +1868,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1858,22 +1885,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1885,10 +1912,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1897,7 +1924,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -1905,22 +1932,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1932,10 +1959,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1944,7 +1971,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -1952,7 +1979,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1964,10 +1991,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -1982,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -1999,25 +2026,25 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2026,7 +2053,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2038,7 +2065,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2046,25 +2073,25 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2073,10 +2100,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2085,33 +2112,33 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2120,7 +2147,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -2132,7 +2159,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2140,25 +2167,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2167,10 +2194,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2179,34 +2206,34 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
       </c>
@@ -2214,7 +2241,7 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -2226,7 +2253,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2234,25 +2261,25 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2261,10 +2288,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2273,10 +2300,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2292,23 +2319,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2316,16 +2343,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2336,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2344,7 +2371,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2357,7 +2384,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2365,7 +2392,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2396,12 +2423,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -2415,7 +2442,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2425,25 +2452,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2460,13 +2487,13 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2478,7 +2505,7 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2486,13 +2513,13 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -2504,21 +2531,21 @@
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="Q11">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2530,53 +2557,53 @@
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="Q12">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H14">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2584,7 +2611,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2592,7 +2619,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2600,7 +2627,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2608,10 +2635,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2619,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2627,72 +2654,72 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2703,7 +2730,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>41</v>
@@ -2711,58 +2738,58 @@
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
